--- a/input/sample_data_model.xlsx
+++ b/input/sample_data_model.xlsx
@@ -7,13 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Entities" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tables" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Columns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Relationships" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mappings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Lookups" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ChangeLog" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,16 +462,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -615,7 +610,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Reference data</t>
+          <t>Reference / lookup data</t>
         </is>
       </c>
     </row>
@@ -648,7 +643,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1999,1358 +1994,6 @@
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00375623"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>From Entity</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>To Entity</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Cardinality</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>1..N</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>places</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>OrderItem</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>1..N</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>contains</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>OrderItem</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1..N</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>included in</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>OrderStatus</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>1..N</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>classifies</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00833C00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Source System</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Source Table</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Source Column</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Target Entity</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Target Column</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Transformation</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>crm_accounts</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>account_id</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>customer_code</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>CAST(account_id AS STRING)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Natural key from CRM</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>crm_accounts</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>TRIM(name)</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>crm_accounts</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>email_address</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>LOWER(email_address)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Normalise to lowercase</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>crm_accounts</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>REGEXP_REPLACE(phone_number, '[^0-9+]', '')</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Strip non-numeric</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>crm_accounts</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>country_code</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>UPPER(LEFT(country, 2))</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>ISO-2 from full name — verify mapping</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>OMS</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>order_ref</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>CONCAT('ORD-', LPAD(CAST(id AS STRING), 10, '0'))</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Pad to 10 digits</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>OMS</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>cust_id</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>customer_id</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Lookup via customer_code</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Join to Customer on code</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>OMS</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>status_code</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>UPPER(status)</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>OMS</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>placed_date</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>order_date</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>DATE(placed_date)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>OMS</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>order_lines</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>OrderItem</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>OMS</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>order_lines</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>prod_sku</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>OrderItem</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>product_id</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Lookup via Product.sku</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Join to Product on sku</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>OMS</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>order_lines</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>qty</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>OrderItem</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>CAST(qty AS INT64)</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>OMS</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>order_lines</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>OrderItem</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>unit_price</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>ROUND(price, 2)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2 decimal places</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>PIM</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>products</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>sku</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>sku</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>UPPER(TRIM(sku))</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>PIM</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>products</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>product_name</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>TRIM(title)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>PIM</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>products</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>category_name</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>PIM</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>products</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>cost_price</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>unit_cost</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>CAST(cost_price AS NUMERIC)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>PIM</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>products</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>active_flag</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>is_active</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>CAST(active_flag AS BOOL)</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>0/1 → FALSE/TRUE</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="007030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>OrderStatus</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Order received, awaiting payment confirmation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>OrderStatus</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Payment confirmed, order being processed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>OrderStatus</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SHIPPED</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Order dispatched to carrier</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>OrderStatus</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>DELIVERED</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Order delivered to customer — terminal state</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>OrderStatus</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>CANCELLED</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Cancelled</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Order cancelled — terminal state</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>OrderStatus</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>REFUNDED</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Refunded</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Order refunded — terminal state</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00404040"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Author</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>J. Smith</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Initial draft — Customer and Order entities</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>A. Lee</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Added OrderItem and Product; first mapping pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>J. Smith</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Added OrderStatus lookup; updated FK references</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Data Team</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>First complete draft submitted for architecture review</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00FF0000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Open Question</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Should line_total be stored or always derived?</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Data Team</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Open Question</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Confirm ISO currency codes — CRM uses 3-char, OMS uses symbol</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>J. Smith</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Partitioning strategy for Order table — by order_date?</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>dbt version to use — Core 1.8 or Cloud?</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>customer_code is stable and can be used as a join key across systems</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Data Team</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>PIM system does not provide created_at — will default to load time</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>A. Lee</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Legend:</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Open = unresolved | TBD = needs decision | Assumption = flagged | Note = informational</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
